--- a/Harbour Survey/raw data/2026/hs-0623-26.xlsx
+++ b/Harbour Survey/raw data/2026/hs-0623-26.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ktheus\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\YYLB3EQ2\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="P:\tech\Archived Harbour data\HS2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62D7F6C3-FDA5-4A9D-8AB4-8EBB4E84963C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57DA5814-1CED-43DC-A950-7787B5B13DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="397" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1949,7 +1949,7 @@
     </row>
     <row r="2" spans="1:37" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="151">
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="C2" s="152"/>
       <c r="D2" s="152"/>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E2" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F2" s="109">
         <f>Report!$C$51</f>
@@ -5526,7 +5526,7 @@
       </c>
       <c r="N2" s="110">
         <f>E2+F2</f>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O2" t="str">
         <f>"River: Flow = " &amp;Report!H59</f>
@@ -5552,7 +5552,7 @@
       </c>
       <c r="E3" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F3" s="109">
         <f>Report!$C$51</f>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="N3" s="110">
         <f t="shared" ref="N3:N66" si="0">E3+F3</f>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O3" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="E4" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F4" s="109">
         <f>Report!$C$51</f>
@@ -5650,7 +5650,7 @@
       </c>
       <c r="N4" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O4" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -5676,7 +5676,7 @@
       </c>
       <c r="E5" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F5" s="109">
         <f>Report!$C$51</f>
@@ -5712,7 +5712,7 @@
       </c>
       <c r="N5" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O5" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="E6" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F6" s="109">
         <f>Report!$C$51</f>
@@ -5774,7 +5774,7 @@
       </c>
       <c r="N6" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O6" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="E7" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F7" s="109">
         <f>Report!$C$51</f>
@@ -5836,7 +5836,7 @@
       </c>
       <c r="N7" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O7" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="E8" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F8" s="109">
         <f>Report!$C$51</f>
@@ -5898,7 +5898,7 @@
       </c>
       <c r="N8" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O8" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -5924,7 +5924,7 @@
       </c>
       <c r="E9" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F9" s="109">
         <f>Report!$C$51</f>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="N9" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O9" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -5986,7 +5986,7 @@
       </c>
       <c r="E10" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F10" s="109">
         <f>Report!$C$51</f>
@@ -6022,7 +6022,7 @@
       </c>
       <c r="N10" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O10" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -6048,7 +6048,7 @@
       </c>
       <c r="E11" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F11" s="109">
         <f>Report!$C$51</f>
@@ -6084,7 +6084,7 @@
       </c>
       <c r="N11" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O11" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -6110,7 +6110,7 @@
       </c>
       <c r="E12" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F12" s="109">
         <f>Report!$C$51</f>
@@ -6146,7 +6146,7 @@
       </c>
       <c r="N12" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O12" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -6172,7 +6172,7 @@
       </c>
       <c r="E13" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F13" s="109">
         <f>Report!$C$51</f>
@@ -6208,7 +6208,7 @@
       </c>
       <c r="N13" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O13" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="E14" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F14" s="109">
         <f>Report!$C$51</f>
@@ -6270,7 +6270,7 @@
       </c>
       <c r="N14" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O14" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E15" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F15" s="109">
         <f>Report!$C$51</f>
@@ -6332,7 +6332,7 @@
       </c>
       <c r="N15" s="110">
         <f t="shared" si="0"/>
-        <v>46190.378472222219</v>
+        <v>46196.378472222219</v>
       </c>
       <c r="O15" t="str">
         <f>TRIM("Outfall: "&amp;Report!$C$52&amp;" "&amp;Report!$C$53&amp;" "&amp;Report!$C$54&amp;" "&amp;Report!$C$55)</f>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="E16" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F16" s="109">
         <f>Report!$J$51</f>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="N16" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O16" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6420,7 +6420,7 @@
       </c>
       <c r="E17" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F17" s="109">
         <f>Report!$J$51</f>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="N17" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O17" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6482,7 +6482,7 @@
       </c>
       <c r="E18" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F18" s="109">
         <f>Report!$J$51</f>
@@ -6518,7 +6518,7 @@
       </c>
       <c r="N18" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O18" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="E19" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F19" s="109">
         <f>Report!$J$51</f>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="N19" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O19" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6606,7 +6606,7 @@
       </c>
       <c r="E20" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F20" s="109">
         <f>Report!$J$51</f>
@@ -6642,7 +6642,7 @@
       </c>
       <c r="N20" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O20" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="E21" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F21" s="109">
         <f>Report!$J$51</f>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="N21" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O21" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="E22" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F22" s="109">
         <f>Report!$J$51</f>
@@ -6766,7 +6766,7 @@
       </c>
       <c r="N22" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O22" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6792,7 +6792,7 @@
       </c>
       <c r="E23" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F23" s="109">
         <f>Report!$J$51</f>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="N23" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O23" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6854,7 +6854,7 @@
       </c>
       <c r="E24" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F24" s="109">
         <f>Report!$J$51</f>
@@ -6890,7 +6890,7 @@
       </c>
       <c r="N24" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O24" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6916,7 +6916,7 @@
       </c>
       <c r="E25" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F25" s="109">
         <f>Report!$J$51</f>
@@ -6952,7 +6952,7 @@
       </c>
       <c r="N25" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O25" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -6978,7 +6978,7 @@
       </c>
       <c r="E26" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F26" s="109">
         <f>Report!$J$51</f>
@@ -7014,7 +7014,7 @@
       </c>
       <c r="N26" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O26" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -7040,7 +7040,7 @@
       </c>
       <c r="E27" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F27" s="109">
         <f>Report!$J$51</f>
@@ -7076,7 +7076,7 @@
       </c>
       <c r="N27" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O27" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -7102,7 +7102,7 @@
       </c>
       <c r="E28" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F28" s="109">
         <f>Report!$J$51</f>
@@ -7138,7 +7138,7 @@
       </c>
       <c r="N28" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O28" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -7164,7 +7164,7 @@
       </c>
       <c r="E29" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F29" s="109">
         <f>Report!$J$51</f>
@@ -7200,7 +7200,7 @@
       </c>
       <c r="N29" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O29" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -7226,7 +7226,7 @@
       </c>
       <c r="E30" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F30" s="109">
         <f>Report!$J$51</f>
@@ -7262,7 +7262,7 @@
       </c>
       <c r="N30" s="110">
         <f t="shared" si="0"/>
-        <v>46190.395833333336</v>
+        <v>46196.395833333336</v>
       </c>
       <c r="O30" t="str">
         <f>TRIM("Hohm: "&amp;Report!$J$52&amp;" "&amp;Report!$J$53&amp;" "&amp;Report!$J$54&amp;" "&amp;Report!$J$55)</f>
@@ -7288,7 +7288,7 @@
       </c>
       <c r="E31" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F31" s="109">
         <f>Report!$C$27</f>
@@ -7324,7 +7324,7 @@
       </c>
       <c r="N31" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O31" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7350,7 +7350,7 @@
       </c>
       <c r="E32" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F32" s="109">
         <f>Report!$C$27</f>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="N32" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O32" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7412,7 +7412,7 @@
       </c>
       <c r="E33" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F33" s="109">
         <f>Report!$C$27</f>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="N33" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O33" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7474,7 +7474,7 @@
       </c>
       <c r="E34" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F34" s="109">
         <f>Report!$C$27</f>
@@ -7510,7 +7510,7 @@
       </c>
       <c r="N34" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O34" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="E35" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F35" s="109">
         <f>Report!$C$27</f>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="N35" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O35" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7598,7 +7598,7 @@
       </c>
       <c r="E36" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F36" s="109">
         <f>Report!$C$27</f>
@@ -7634,7 +7634,7 @@
       </c>
       <c r="N36" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O36" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7660,7 +7660,7 @@
       </c>
       <c r="E37" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F37" s="109">
         <f>Report!$C$27</f>
@@ -7696,7 +7696,7 @@
       </c>
       <c r="N37" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O37" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="E38" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F38" s="109">
         <f>Report!$C$27</f>
@@ -7758,7 +7758,7 @@
       </c>
       <c r="N38" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O38" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7784,7 +7784,7 @@
       </c>
       <c r="E39" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F39" s="109">
         <f>Report!$C$27</f>
@@ -7820,7 +7820,7 @@
       </c>
       <c r="N39" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O39" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="E40" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F40" s="109">
         <f>Report!$C$27</f>
@@ -7882,7 +7882,7 @@
       </c>
       <c r="N40" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O40" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="E41" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F41" s="109">
         <f>Report!$C$27</f>
@@ -7944,7 +7944,7 @@
       </c>
       <c r="N41" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O41" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -7970,7 +7970,7 @@
       </c>
       <c r="E42" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F42" s="109">
         <f>Report!$C$27</f>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="N42" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O42" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -8032,7 +8032,7 @@
       </c>
       <c r="E43" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F43" s="109">
         <f>Report!$C$27</f>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="N43" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O43" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -8094,7 +8094,7 @@
       </c>
       <c r="E44" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F44" s="109">
         <f>Report!$C$27</f>
@@ -8130,7 +8130,7 @@
       </c>
       <c r="N44" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O44" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -8156,7 +8156,7 @@
       </c>
       <c r="E45" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F45" s="109">
         <f>Report!$C$27</f>
@@ -8192,7 +8192,7 @@
       </c>
       <c r="N45" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O45" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="E46" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F46" s="109">
         <f>Report!$C$27</f>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="N46" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O46" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -8280,7 +8280,7 @@
       </c>
       <c r="E47" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F47" s="109">
         <f>Report!$C$27</f>
@@ -8316,7 +8316,7 @@
       </c>
       <c r="N47" s="110">
         <f t="shared" si="0"/>
-        <v>46190.430555555555</v>
+        <v>46196.430555555555</v>
       </c>
       <c r="O47" t="str">
         <f>TRIM("Polly: "&amp;Report!$J$25&amp;" "&amp;Report!J$26&amp;" "&amp;Report!$J$27&amp;" "&amp;Report!$J$28)</f>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="E48" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F48" s="109">
         <f>Report!$J$24</f>
@@ -8378,7 +8378,7 @@
       </c>
       <c r="N48" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O48" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8404,7 +8404,7 @@
       </c>
       <c r="E49" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F49" s="109">
         <f>Report!$J$24</f>
@@ -8440,7 +8440,7 @@
       </c>
       <c r="N49" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O49" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8466,7 +8466,7 @@
       </c>
       <c r="E50" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F50" s="109">
         <f>Report!$J$24</f>
@@ -8502,7 +8502,7 @@
       </c>
       <c r="N50" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O50" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8528,7 +8528,7 @@
       </c>
       <c r="E51" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F51" s="109">
         <f>Report!$J$24</f>
@@ -8564,7 +8564,7 @@
       </c>
       <c r="N51" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O51" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="E52" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F52" s="109">
         <f>Report!$J$24</f>
@@ -8626,7 +8626,7 @@
       </c>
       <c r="N52" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O52" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="E53" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F53" s="109">
         <f>Report!$J$24</f>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="N53" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O53" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8714,7 +8714,7 @@
       </c>
       <c r="E54" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F54" s="109">
         <f>Report!$J$24</f>
@@ -8750,7 +8750,7 @@
       </c>
       <c r="N54" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O54" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8776,7 +8776,7 @@
       </c>
       <c r="E55" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F55" s="109">
         <f>Report!$J$24</f>
@@ -8812,7 +8812,7 @@
       </c>
       <c r="N55" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O55" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="E56" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F56" s="109">
         <f>Report!$J$24</f>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="N56" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O56" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="E57" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F57" s="109">
         <f>Report!$J$24</f>
@@ -8936,7 +8936,7 @@
       </c>
       <c r="N57" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O57" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -8962,7 +8962,7 @@
       </c>
       <c r="E58" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F58" s="109">
         <f>Report!$J$24</f>
@@ -8998,7 +8998,7 @@
       </c>
       <c r="N58" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O58" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="E59" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F59" s="109">
         <f>Report!$J$24</f>
@@ -9060,7 +9060,7 @@
       </c>
       <c r="N59" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O59" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9086,7 +9086,7 @@
       </c>
       <c r="E60" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F60" s="109">
         <f>Report!$J$24</f>
@@ -9122,7 +9122,7 @@
       </c>
       <c r="N60" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O60" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9148,7 +9148,7 @@
       </c>
       <c r="E61" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F61" s="109">
         <f>Report!$J$24</f>
@@ -9184,7 +9184,7 @@
       </c>
       <c r="N61" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O61" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9210,7 +9210,7 @@
       </c>
       <c r="E62" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F62" s="109">
         <f>Report!$J$24</f>
@@ -9246,7 +9246,7 @@
       </c>
       <c r="N62" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O62" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9272,7 +9272,7 @@
       </c>
       <c r="E63" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F63" s="109">
         <f>Report!$J$24</f>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="N63" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O63" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9334,7 +9334,7 @@
       </c>
       <c r="E64" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F64" s="109">
         <f>Report!$J$24</f>
@@ -9370,7 +9370,7 @@
       </c>
       <c r="N64" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O64" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9396,7 +9396,7 @@
       </c>
       <c r="E65" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F65" s="109">
         <f>Report!$J$24</f>
@@ -9432,7 +9432,7 @@
       </c>
       <c r="N65" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O65" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="E66" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F66" s="109">
         <f>Report!$J$24</f>
@@ -9494,7 +9494,7 @@
       </c>
       <c r="N66" s="110">
         <f t="shared" si="0"/>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O66" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
@@ -9520,7 +9520,7 @@
       </c>
       <c r="E67" s="108">
         <f>Report!$B$2</f>
-        <v>46190</v>
+        <v>46196</v>
       </c>
       <c r="F67" s="109">
         <f>Report!$J$24</f>
@@ -9556,7 +9556,7 @@
       </c>
       <c r="N67" s="110">
         <f t="shared" ref="N67" si="1">E67+F67</f>
-        <v>46190.409722222219</v>
+        <v>46196.409722222219</v>
       </c>
       <c r="O67" t="str">
         <f>TRIM("5KM: "&amp;Report!$C$28&amp;" "&amp;Report!$C$29&amp;" "&amp;Report!$C$30&amp;" "&amp;Report!$C$31)</f>
